--- a/output/pdf_financials_xlsx/GMA.xlsx
+++ b/output/pdf_financials_xlsx/GMA.xlsx
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.4875</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.354227</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.214415</v>
+        <v>-4.829389</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>1.337503</v>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.24375</v>
+        <v>-2.24375</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.638798</v>
+        <v>-0.638798</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.307487</v>
+        <v>-2.307487</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.588945</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.24375</v>
+        <v>-2.24375</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.638798</v>
+        <v>-0.638798</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.307487</v>
+        <v>-2.307487</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-1.588945</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11.809211</v>
+        <v>-11.809211</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.992488</v>
+        <v>-3.992488</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-57.687175</v>
+        <v>57.687175</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>66.206042</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>8.871144057450179</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.502114673766069</v>
+        <v>191.4978853262339</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>62.46021235023592</v>
@@ -5592,13 +5592,13 @@
         <v>4.424649</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>4.524149</v>
+        <v>5.676686</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>4.775095</v>
+        <v>5.7658</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>5.020368</v>
+        <v>6.187715</v>
       </c>
     </row>
     <row r="93">
@@ -10356,7 +10356,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -51022,10 +51026,10 @@
         </is>
       </c>
       <c r="J482" s="5" t="n">
-        <v>2.307487</v>
+        <v>-2.307487</v>
       </c>
       <c r="K482" s="5" t="n">
-        <v>1.967265</v>
+        <v>-1.967265</v>
       </c>
       <c r="L482" t="inlineStr">
         <is>
@@ -52729,10 +52733,10 @@
         </is>
       </c>
       <c r="F501" s="5" t="n">
-        <v>2.24375</v>
+        <v>-2.24375</v>
       </c>
       <c r="G501" s="5" t="n">
-        <v>0.638798</v>
+        <v>-0.638798</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GMA.xlsx
+++ b/output/pdf_financials_xlsx/GMA.xlsx
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015329</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004731</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.521902</v>
+        <v>2.537231</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.141368</v>
+        <v>2.146099</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.212183</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.521902</v>
+        <v>2.537231</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.201409</v>
+        <v>2.20614</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.154841</v>
@@ -2504,7 +2504,7 @@
         <v>0.08069</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.726786</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.48578</v>
@@ -2608,7 +2608,7 @@
         <v>0.22847</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.726786</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.48578</v>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.794974</v>
+        <v>0.068188</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.194785</v>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -50538,7 +50538,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">

--- a/output/pdf_financials_xlsx/GMA.xlsx
+++ b/output/pdf_financials_xlsx/GMA.xlsx
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.010264</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.026545</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.007442</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.060041</v>
@@ -2170,16 +2170,16 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.08029500000000001</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.094305</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.181614</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.15079</v>
       </c>
     </row>
     <row r="29">
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.262815</v>
+        <v>2.273079</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.023257</v>
+        <v>4.049802</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.537231</v>
+        <v>2.544673</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>2.20614</v>
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.442774</v>
+        <v>-1.362479</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.400872</v>
+        <v>-1.306567</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.022401</v>
+        <v>-1.840787</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.584724</v>
+        <v>-2.433934</v>
       </c>
     </row>
     <row r="30">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1094.096413865276</v>
+        <v>-1033.206439724272</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-234.0755593429913</v>
+        <v>-218.3178772536635</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.010264</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.059863</v>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.007442</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -5968,22 +5968,22 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.056253</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.098995</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.11236</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.128416</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.423401</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.345529</v>
       </c>
     </row>
     <row r="101">
@@ -6658,16 +6658,16 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.194501</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -26966,7 +26966,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -27324,7 +27328,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30601,7 +30609,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32221,7 +32233,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -32842,7 +32858,11 @@
           <t>Proceeds from disposal of property, and equipment</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -35896,7 +35916,11 @@
           <t>Proceed from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -38171,7 +38195,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -39811,7 +39839,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -42990,7 +43022,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -43077,7 +43113,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -45644,7 +45684,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -50267,7 +50311,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -51990,7 +52038,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
